--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -34,8 +34,11 @@
     <sheet name="SERIES" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="CLUBS" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="META" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$12</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -43,7 +46,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +61,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +88,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +116,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24264,7 +24282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -24315,6 +24333,163 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0048 'ČKD Praha Stalingrad' ROZBITÝ prev CLUB_S1950_51_0245 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0052 'ČKD Kutná Hora' ROZBITÝ prev CLUB_S1950_51_0097 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0063 'Sokol Kyšice' prev→CLUB_S1951_52_0088 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0149 'Sokol Osek' ROZBITÝ prev CLUB_S1950_51_0013 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0328 'Sokol Sukno Humpolec' ROZBITÝ prev CLUB_S1950_51_0760 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1952_53_0329 'Sokol Sukno Humpolec B' ROZBITÝ prev CLUB_S1950_51_0768 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0023</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0023 'Ústecký O postup do KP' (L25, parent=NODE_S1952_53_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0036</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0036 'Jihlavský Kvalifikace o KP' (L25, parent=NODE_S1952_53_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0043</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0043 'Gottwaldovský kvalifikace' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0046</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0046 'Gottwaldovský Kvalifikace o postup do KP' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0048</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0048 'Olomoucký kvalifikace o KP' (L25, parent=NODE_S1952_53_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -51486,6 +51661,303 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0048</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0048 'ČKD Praha Stalingrad' ROZBITÝ prev CLUB_S1950_51_0245 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0052</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0052 'ČKD Kutná Hora' ROZBITÝ prev CLUB_S1950_51_0097 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0063</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0063 'Sokol Kyšice' prev→CLUB_S1951_52_0088 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0149</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0149 'Sokol Osek' ROZBITÝ prev CLUB_S1950_51_0013 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0328</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0328 'Sokol Sukno Humpolec' ROZBITÝ prev CLUB_S1950_51_0760 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0329</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0329 'Sokol Sukno Humpolec B' ROZBITÝ prev CLUB_S1950_51_0768 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0023</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1952_53_0023 'Ústecký O postup do KP' (L25, parent=NODE_S1952_53_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0036</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1952_53_0036 'Jihlavský Kvalifikace o KP' (L25, parent=NODE_S1952_53_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0043</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1952_53_0043 'Gottwaldovský kvalifikace' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0046</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1952_53_0046 'Gottwaldovský Kvalifikace o postup do KP' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S1952_53_0048</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1952_53_0048 'Olomoucký kvalifikace o KP' (L25, parent=NODE_S1952_53_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -37,7 +37,7 @@
     <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24282,7 +24282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -24339,7 +24339,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0048 'ČKD Praha Stalingrad' ROZBITÝ prev CLUB_S1950_51_0245 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl ČSA Rynholec' → 'Rynholec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -24351,7 +24351,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0052 'ČKD Kutná Hora' ROZBITÝ prev CLUB_S1950_51_0097 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -24363,7 +24363,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0063 'Sokol Kyšice' prev→CLUB_S1951_52_0088 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -24375,7 +24375,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0149 'Sokol Osek' ROZBITÝ prev CLUB_S1950_51_0013 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -24387,7 +24387,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0328 'Sokol Sukno Humpolec' ROZBITÝ prev CLUB_S1950_51_0760 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24399,7 +24399,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1952_53_0329 'Sokol Sukno Humpolec B' ROZBITÝ prev CLUB_S1950_51_0768 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24409,14 +24409,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NODE_S1952_53_0023</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0023 'Ústecký O postup do KP' (L25, parent=NODE_S1952_53_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24426,14 +24421,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NODE_S1952_53_0036</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0036 'Jihlavský Kvalifikace o KP' (L25, parent=NODE_S1952_53_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24443,14 +24433,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NODE_S1952_53_0043</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0043 'Gottwaldovský kvalifikace' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24460,14 +24445,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NODE_S1952_53_0046</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0046 'Gottwaldovský Kvalifikace o postup do KP' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24477,17 +24457,72 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NODE_S1952_53_0048</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1952_53_0048 'Olomoucký kvalifikace o KP' (L25, parent=NODE_S1952_53_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: BZGK = neznámá zkratka. K vyřešení.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -30219,12 +30254,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Rynholec = Banik Rynholec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Rakovník). Důl ČSA Rynholec = hornicky podnik. city Rynholec.</t>
+          <t>Rynholec = Banik Rynholec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Rakovník). Důl ČSA Rynholec = hornicky podnik. city Rynholec. || TBD: city 'Důl ČSA Rynholec' → 'Rynholec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Důl ČSA Rynholec</t>
+          <t>Rynholec</t>
         </is>
       </c>
     </row>
@@ -30360,12 +30395,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — rod BOHEMIANS: AFK Bohemians → Železničáři Praha → DSO Spartak Praha Stalingrad → TJ ČKD Praha → TJ Bohemians ČKD Praha → TJ Bohemians Praha. 52/53 navazuje na 50/51 0245 „ČKD Stalingrad (Sokol Vysočany)" přes mezeru 51/52. city: Praha Stalingrad → „Praha". || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — rod BOHEMIANS: AFK Bohemians → Železničáři Praha → DSO Spartak Praha Stalingrad → TJ ČKD Praha → TJ Bohemians ČKD Praha → TJ Bohemians Praha. 52/53 navazuje na 50/51 0245 „ČKD Stalingrad (Sokol Vysočany)" přes mezeru 51/52. city: Praha Stalingrad → „Praha". || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Praha Stalingrad</t>
         </is>
       </c>
     </row>
@@ -32688,12 +32723,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>České Budějovice = HC Motor České Budějovice (Wiki D42 - registr ustavy 04/2026). Vsechny ceskobudějovicke kluby. Hlavni chain: AC Stadion ČB -&gt; Slavoj ČB -&gt; TJ Motor ČB (1965+, podnik Motor) -&gt; HC Motor ČB. Plus paralelni: DA České Budějovice (Doprava arm), PDA II. ČB (poucovatelska), ZSJ Slavia ČB. city České Budějovice.</t>
+          <t>České Budějovice = HC Motor České Budějovice (Wiki D42 - registr ustavy 04/2026). Vsechny ceskobudějovicke kluby. Hlavni chain: AC Stadion ČB -&gt; Slavoj ČB -&gt; TJ Motor ČB (1965+, podnik Motor) -&gt; HC Motor ČB. Plus paralelni: DA České Budějovice (Doprava arm), PDA II. ČB (poucovatelska), ZSJ Slavia ČB. city České Budějovice. || TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Budvar České Budějovice</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -40991,12 +41026,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>RD Svobodné Dvory 52/53 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové.</t>
+          <t>RD Svobodné Dvory 52/53 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové. || TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Svobodné Dvory</t>
         </is>
       </c>
     </row>
@@ -45519,12 +45554,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová.</t>
+          <t>Moravská Třebová = Slovan/Slavoj Moravská Třebová (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Svitavy). POZOR: NE Třebová Česká (Pardubicky), NE Trebon (Jihocesky). city Moravská Třebová. || TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová</t>
+          <t>Moravská Třebová</t>
         </is>
       </c>
     </row>
@@ -45897,12 +45932,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>city: tehdejší úřední „Gottwaldov" → moderní „Zlín" (Pavlovo rozhodnutí 04/2026 — clean_name zachovává dobový název, city moderní pro orientaci). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín.</t>
+          <t>city: tehdejší úřední „Gottwaldov" → moderní „Zlín" (Pavlovo rozhodnutí 04/2026 — clean_name zachovává dobový název, city moderní pro orientaci). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín. || TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>I. Gottwaldov</t>
         </is>
       </c>
     </row>
@@ -50020,12 +50055,12 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -50896,9 +50931,14 @@
           <t>CLUB_S1951_52_0451</t>
         </is>
       </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Gottwald H. Suchá</t>
+          <t>Suchá</t>
         </is>
       </c>
     </row>
@@ -51671,11 +51711,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -51720,21 +51760,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0048</t>
+          <t>CLUB_S1952_53_0045</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0048 'ČKD Praha Stalingrad' ROZBITÝ prev CLUB_S1950_51_0245 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Důl ČSA Rynholec' → 'Rynholec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -51742,21 +51780,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0052</t>
+          <t>CLUB_S1952_53_0048</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0052 'ČKD Kutná Hora' ROZBITÝ prev CLUB_S1950_51_0097 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -51764,7 +51800,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -51774,11 +51810,9 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0063 'Sokol Kyšice' prev→CLUB_S1951_52_0088 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -51786,21 +51820,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0149</t>
+          <t>CLUB_S1952_53_0092</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0149 'Sokol Osek' ROZBITÝ prev CLUB_S1950_51_0013 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -51808,21 +51840,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0328</t>
+          <t>CLUB_S1952_53_0093</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0328 'Sokol Sukno Humpolec' ROZBITÝ prev CLUB_S1950_51_0760 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -51830,21 +51860,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0329</t>
+          <t>CLUB_S1952_53_0102</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0329 'Sokol Sukno Humpolec B' ROZBITÝ prev CLUB_S1950_51_0768 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -51852,21 +51880,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NODE_S1952_53_0023</t>
+          <t>CLUB_S1952_53_0213</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1952_53_0023 'Ústecký O postup do KP' (L25, parent=NODE_S1952_53_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -51874,21 +51900,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NODE_S1952_53_0036</t>
+          <t>CLUB_S1952_53_0235</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1952_53_0036 'Jihlavský Kvalifikace o KP' (L25, parent=NODE_S1952_53_0035) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -51896,21 +51920,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NODE_S1952_53_0043</t>
+          <t>CLUB_S1952_53_0291</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1952_53_0043 'Gottwaldovský kvalifikace' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -51918,21 +51940,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NODE_S1952_53_0046</t>
+          <t>CLUB_S1952_53_0336</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1952_53_0046 'Gottwaldovský Kvalifikace o postup do KP' (L25, parent=NODE_S1952_53_0042) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -51940,24 +51960,122 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S1952_53_0048</t>
+          <t>CLUB_S1952_53_0397</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1952_53_0048 'Olomoucký kvalifikace o KP' (L25, parent=NODE_S1952_53_0047) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0406</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0500</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0513</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>TBD: BZGK = neznámá zkratka. K vyřešení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0513</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1952_53_0519</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -37,7 +37,7 @@
     <sheet name="TODO" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'TODO'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24282,7 +24282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -24351,7 +24351,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -24363,7 +24363,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -24375,7 +24375,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -24387,7 +24387,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24399,7 +24399,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24411,7 +24411,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24423,7 +24423,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24435,7 +24435,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24447,7 +24447,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24459,7 +24459,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: BZGK = neznámá zkratka. K vyřešení.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -24471,7 +24471,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -24483,46 +24483,10 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: BZGK = neznámá zkratka. K vyřešení.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24670,7 +24634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24729,6 +24693,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24771,6 +24740,11 @@
           <t>3 sk.×7 + finále A (top6) + finále B (7.-12.). Sestup: Holoubkov, Kladno, Prostějov, Opava, Žilina.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24823,6 +24797,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24875,6 +24854,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24927,6 +24911,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25441,6 +25430,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25483,6 +25477,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0024</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25525,6 +25524,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25693,6 +25697,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0027</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25866,6 +25875,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0029</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -26034,6 +26048,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0032</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26202,6 +26221,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0034</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26244,6 +26268,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26333,6 +26362,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26375,6 +26409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26417,6 +26456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26501,6 +26545,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26543,6 +26592,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0042</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26773,6 +26827,11 @@
           <t>Kontejner L20</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26860,6 +26919,11 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>Kontejner L20</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1951_52_0044</t>
         </is>
       </c>
     </row>
@@ -30395,12 +30459,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — rod BOHEMIANS: AFK Bohemians → Železničáři Praha → DSO Spartak Praha Stalingrad → TJ ČKD Praha → TJ Bohemians ČKD Praha → TJ Bohemians Praha. 52/53 navazuje na 50/51 0245 „ČKD Stalingrad (Sokol Vysočany)" přes mezeru 51/52. city: Praha Stalingrad → „Praha". || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — rod BOHEMIANS: AFK Bohemians → Železničáři Praha → DSO Spartak Praha Stalingrad → TJ ČKD Praha → TJ Bohemians ČKD Praha → TJ Bohemians Praha. 52/53 navazuje na 50/51 0245 „ČKD Stalingrad (Sokol Vysočany)" přes mezeru 51/52. city: Praha Stalingrad → „Praha". || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Praha Stalingrad</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -41026,12 +41090,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>RD Svobodné Dvory 52/53 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové. || TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>RD Svobodné Dvory 52/53 (20_Královéhradecký). SK Meteor / Slavoj Svobodné Dvory (Wiki D42 - Pavlovo upresneni 04/2026). Genealogie: SK Meteor Svobodné Dvory (1934-48) -&gt; Sokol Meteor Svobodné Dvory (1948-49) -&gt; ZSJ RDP Svobodné Dvory (1949, RDP = Rolnicky druzstevni podnik) -&gt; ZSJ RDP Hradec Králové (1950-51) -&gt; RDP Svobodné Dvory (1952-53) -&gt; [pauza] -&gt; Slavoj Svobodné Dvory (1958-59 az 1968-69, stabilni v KP/krajske soutezi). Svobodné Dvory = dnes čtvrť HK od 1942/54 (D37). city Hradec Králové. Samostatný klub, NE Spartak HK chain. || Hradec Králové = vsechny hradecke kluby (Wiki D42 - registr ustavy 04/2026). RDP Svobodné Dvory = Rolnicky druzstevni podnik. Soucasti hradeckeho chain. city Hradec Králové.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Svobodné Dvory</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -45932,12 +45996,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>city: tehdejší úřední „Gottwaldov" → moderní „Zlín" (Pavlovo rozhodnutí 04/2026 — clean_name zachovává dobový název, city moderní pro orientaci). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín. || TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>city: tehdejší úřední „Gottwaldov" → moderní „Zlín" (Pavlovo rozhodnutí 04/2026 — clean_name zachovává dobový název, city moderní pro orientaci). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>I. Gottwaldov</t>
+          <t>Zlín</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51785,12 +51849,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0048</t>
+          <t>CLUB_S1952_53_0063</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'Praha Stalingrad' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51805,12 +51869,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0063</t>
+          <t>CLUB_S1952_53_0092</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
         </is>
       </c>
     </row>
@@ -51825,12 +51889,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0092</t>
+          <t>CLUB_S1952_53_0093</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
+          <t>TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
         </is>
       </c>
     </row>
@@ -51845,12 +51909,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0093</t>
+          <t>CLUB_S1952_53_0102</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
+          <t>TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51865,12 +51929,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0102</t>
+          <t>CLUB_S1952_53_0213</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -51885,12 +51949,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0213</t>
+          <t>CLUB_S1952_53_0235</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -51905,12 +51969,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0235</t>
+          <t>CLUB_S1952_53_0336</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
         </is>
       </c>
     </row>
@@ -51925,12 +51989,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0291</t>
+          <t>CLUB_S1952_53_0397</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec Králové' → 'Svobodné Dvory' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51945,12 +52009,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0336</t>
+          <t>CLUB_S1952_53_0500</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51965,12 +52029,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0397</t>
+          <t>CLUB_S1952_53_0513</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: BZGK = neznámá zkratka. K vyřešení.</t>
         </is>
       </c>
     </row>
@@ -51985,12 +52049,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0406</t>
+          <t>CLUB_S1952_53_0513</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Zlín' → 'I. Gottwaldov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -52005,77 +52069,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1952_53_0500</t>
+          <t>CLUB_S1952_53_0519</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CLUB_S1952_53_0513</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>TBD: BZGK = neznámá zkratka. K vyřešení.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CLUB_S1952_53_0513</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S1952_53_0519</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
           <t>TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -24634,7 +24634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24696,6 +24696,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -24958,6 +24958,8 @@
           <t>NODE_S1952_53_0001</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24972,6 +24974,14 @@
         <is>
           <t>Top 2 z každé skupiny</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -25005,6 +25015,8 @@
           <t>NODE_S1952_53_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25019,6 +25031,14 @@
         <is>
           <t>3.-4. z každé skupiny</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -25346,6 +25366,8 @@
           <t>NODE_S1952_53_0008</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25355,6 +25377,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -25655,6 +25685,8 @@
           <t>NODE_S1952_53_0018</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25664,6 +25696,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -26006,6 +26046,8 @@
           <t>NODE_S1952_53_0026</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26015,6 +26057,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -26179,6 +26229,8 @@
           <t>NODE_S1952_53_0030</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26188,6 +26240,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -26545,6 +26605,8 @@
           <t>NODE_S1952_53_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26559,6 +26621,14 @@
         <is>
           <t>NODE_S1951_52_0041</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -27052,6 +27122,8 @@
           <t>NODE_S1952_53_0049</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27061,6 +27133,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -1990,11 +1990,6 @@
           <t>Baník VŽKG Vítkovice</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="F21" t="n">
         <v>12</v>
       </c>
@@ -2605,6 +2600,11 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>Spartak Praha Sokolovo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -24282,7 +24282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -24489,6 +24489,13 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mistrovství republiky 1952/53: základní skupiny → finálový turnaj. Mistr Spartak Praha Sokolovo (před Vítkovicemi). Doloženo PDF i webem.</t>
         </is>
       </c>
     </row>
@@ -24958,8 +24965,6 @@
           <t>NODE_S1952_53_0001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25015,8 +25020,6 @@
           <t>NODE_S1952_53_0001</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25366,8 +25369,6 @@
           <t>NODE_S1952_53_0008</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25685,8 +25686,6 @@
           <t>NODE_S1952_53_0018</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26046,8 +26045,6 @@
           <t>NODE_S1952_53_0026</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26229,8 +26226,6 @@
           <t>NODE_S1952_53_0030</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26605,8 +26600,6 @@
           <t>NODE_S1952_53_0037</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27122,8 +27115,6 @@
           <t>NODE_S1952_53_0049</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -51443,7 +51434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51610,7 +51601,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bez L15 kvalifikace. Civilní krajští přeborníci nemohli postoupit; soutěž byla zúžena na 18 účastníků.</t>
+          <t>Mistr Spartak Praha Sokolovo — vítěz finálového turnaje (1., 9 b) před Vítkovicemi a Č. Budějovicemi (první titul Sparty, hrající trenér Zábrodský). M badge opraven (byl chybně u Baník VŽKG Vítkovice, vítěze základní skupiny). Pozn.: kluby přejmenovány od 12.12.1952 (DSO Baník/Slovan/Tatran…).</t>
         </is>
       </c>
     </row>
@@ -51851,6 +51842,18 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>Žilinský</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TJ Spartak Praha Sokolovo</t>
         </is>
       </c>
     </row>

--- a/data/S1952_53_FINAL.xlsx
+++ b/data/S1952_53_FINAL.xlsx
@@ -24337,21 +24337,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl ČSA Rynholec' → 'Rynholec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mistrovství republiky 1952/53: základní skupiny → finálový turnaj. Mistr Spartak Praha Sokolovo (před Vítkovicemi). Doloženo PDF i webem.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl ČSA Rynholec' → 'Rynholec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -24363,7 +24358,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1951_52_0088 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -24375,7 +24370,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Posázavan" (chybně). PDA = vojenský klub (D33), „Posázavan" by mohla být vojenská posádka v Posázaví, ale lokalita neurčitelná. K vyřešení.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -24387,7 +24382,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. Almanach má „Tankista" (chybně). PDA = vojenský klub (D33), „Tankista" = tankové vojsko (Pardubice/Vyškov/jiné posádky?). K vyřešení.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24399,7 +24394,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Budvar České Budějovice' → 'České Budějovice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24411,7 +24406,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24423,7 +24418,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0210 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24435,7 +24430,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city neznámé. „Rantýře" - název klubu = neznámá obec/lokalita. K vyřešení.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24447,7 +24442,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Moravská Třebová' → 'Moravská Třebová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24459,7 +24454,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: BZGK = neznámá zkratka. K vyřešení.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -24471,7 +24466,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: BZGK = neznámá zkratka. K vyřešení.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -24483,19 +24478,24 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1951_52_0397 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Gottwald H. Suchá' → 'Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Mistrovství republiky 1952/53: základní skupiny → finálový turnaj. Mistr Spartak Praha Sokolovo (před Vítkovicemi). Doloženo PDF i webem.</t>
         </is>
       </c>
     </row>
